--- a/www/download/COUNTRY.CYP.zdW16.xlsx
+++ b/www/download/COUNTRY.CYP.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Chipre</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.06228093212261</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.10033802249269</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.04031951454981</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.885348275453643</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.800589239286038</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.793291509614578</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.784080560245651</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.726795562139051</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.680610883066154</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.714187300943087</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.754317011508633</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.721536836694759</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.777462511474688</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.753325488600873</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.754263085964025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.316</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.324</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.343</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.356</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.369</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.389</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.396</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.394</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.401</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.403</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.389</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.365</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.358</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.243</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.257</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.264</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.276</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.287</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.312</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.324</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.353</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.357</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.344</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.322</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.313</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>555.556</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>570.023</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>575.897</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>609.003</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>609.513</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>620.186</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>637.213</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>658.994</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>687.691</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>685.484</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>654.219</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>648.912</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>623.683</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>584.262</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>569.793</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>423.511</t>
+          <t>477212468.834669</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>436.468</t>
+          <t>563020708.117875</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>446.083</t>
+          <t>626491950.751071</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>458.106</t>
+          <t>669265610.687618</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>462.009</t>
+          <t>604375114.314662</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>472.919</t>
+          <t>591565994.275607</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>497.108</t>
+          <t>540127989.446919</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>519.421</t>
+          <t>570745691.628135</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>556.486</t>
+          <t>681825647.683138</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>554.817</t>
+          <t>584012464.927286</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>557.869</t>
+          <t>534233705.51631</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>560.349</t>
+          <t>522466799.881098</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>470133491.719068</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>506.844</t>
+          <t>449081644.168673</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>492.319</t>
+          <t>437662154.168157</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>222122990.739828</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>250458649.224782</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>301108975.96302</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>352109418.270019</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>349414554.489562</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>340046290.430523</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>316196572.052213</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>312067100.091675</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>366383176.471502</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>319158399.837342</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>322236964.915533</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>314054712.103201</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>283440222.647658</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>276785841.443381</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>269753633.016423</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2446884.02306525</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2514146.44452018</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2400781.26217975</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2251782.98922303</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1996097.90969864</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1816486.93383955</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1630183.85006485</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1383212.53467574</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1424481.42128317</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2088305.64159331</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1115711.8452016</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1059963.13247684</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1179065.91670998</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1258310.29328646</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1329751.67036136</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2018.80023640645</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2014.87376701698</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2030.20474911183</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2454.95428840949</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2698.5255348534</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2953.01524267557</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3123.38577953369</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3617.79578942302</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3996.96978201756</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3646.5275952611</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3852.28427082189</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3912.65563408814</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3566.77885519289</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3198.64884576929</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3062.13968327369</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4328.95645645455</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5032.5666148303</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5641.09633512545</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6560.77171736665</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6529.08939335952</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6902.50160066777</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6659.72930286072</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>7894.15473443603</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10285.5254765527</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>8051.40847152857</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>8137.20342943388</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>8484.97564646326</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>7458.05213985746</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7082.784174137</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>6926.77682516163</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.90665089907806</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.742674894043201</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.481466962495283</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.301033077305237</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.322237422751094</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.390748887162539</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.572148606082651</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.664452932870564</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.518863407865247</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.7383750522711</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.731238376535209</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.784240065201964</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.907414533300245</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.831177481322434</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.825069025001888</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06228093212261</t>
+          <t>914.312137728771</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.10033802249269</t>
+          <t>1003.39990074429</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.04031951454981</t>
+          <t>1171.53908630853</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.885348275453643</t>
+          <t>1331.98191136758</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.800589239286038</t>
+          <t>1267.46428645372</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.793291509614578</t>
+          <t>1185.11933374176</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.784080560245651</t>
+          <t>1061.56104227561</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.726795562139051</t>
+          <t>1000.72825837505</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.680610883066154</t>
+          <t>1126.43170531729</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.714187300943087</t>
+          <t>985.300073590214</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.754317011508633</t>
+          <t>912.464858885835</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.721536836694759</t>
+          <t>879.95156095041</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.777462511474688</t>
+          <t>822.901587062066</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.753325488600873</t>
+          <t>859.583358519815</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.754263085964025</t>
+          <t>860.870059091824</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>132697185.598496</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>229126130.454057</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>293871885.889704</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>356485793.701961</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>338807508.764507</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>317622525.223438</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>260888300.087938</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>284035984.492402</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>313193949.843445</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>265636628.601738</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>216534370.3897</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>254172483.772396</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>253123573.977716</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>291885742.140835</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>312570912.565749</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>194508471.14989</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>246839933.971471</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>303117251.771702</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>332027381.398756</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>241873465.345164</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>202296295.493877</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>149341425.70665</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>131544862.760693</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>187257604.498202</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>127134720.094705</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>100347458.426736</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>101891920.336049</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>79172531.6373224</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>105669256.354545</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>147353210.265091</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-61811285.5513936</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-17713803.5174134</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-9245365.88199865</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>24458412.303205</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>96934043.4193427</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>115326229.729561</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>111546874.381288</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>152491121.731709</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>125936345.345243</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>138501908.507032</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>116186911.962964</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>152280563.436348</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>173951042.340393</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>186216485.78629</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>165217702.300658</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1743.27405943854</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1748.59981571251</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1735.596451638</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1732.95252506147</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1675.88871154962</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1648.20339455616</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1668.93171288525</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1665.6650846588</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1710.89589866568</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1712.82106693011</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1579.69418094294</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1570.04483048473</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1569.61444663802</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1574.04968944099</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1571.14727940003</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1755.86676033792</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1761.99631508907</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1742.71312584779</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1777.85116521703</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1711.44302357966</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1682.95625030325</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1697.51497709287</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1695.42434222714</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1735.23495969836</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1737.77706172557</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1630.33072739152</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1608.3673156658</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1603.42203657665</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1600.67431515498</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1593.78301023333</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3217.07373211893</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3425.62847580159</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3702.11695421729</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4832.6547500896</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6043.50240849727</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6218.05780604376</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6546.45283627106</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>8195.86823393773</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>9186.25075478109</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>8369.77542396845</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>8385.95447176233</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>9113.77175384996</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>8944.1377830699</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>9274.0974952685</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>9346.89364231318</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>62918969.6607777</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>72667346.0638731</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>71216467.3829027</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>73784466.2443506</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>70341034.6891336</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>64640064.0229369</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>58237736.1243792</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>70959120.8568608</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>75823880.6930763</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>54253004.7404267</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>53451345.2154958</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>48789775.8717768</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>50502825.9536773</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>53079968.775897</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>72576649.492372</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5363.79416800817</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5314.54878103561</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5767.95172571949</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>6749.82650004409</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>8029.40094948854</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>8378.67306307562</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>9170.33747744449</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>11219.7583612377</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>14329.6357839471</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>11488.797643079</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>11778.1320877712</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>11872.7662699864</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>11114.1142174602</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>11026.6259872885</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>11067.4404327298</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>555.556</t>
+          <t>489190671.833954</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>570.023</t>
+          <t>570645155.97086</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>575.897</t>
+          <t>660974846.290749</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>609.003</t>
+          <t>689107170.826261</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>609.513</t>
+          <t>653461403.804148</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>620.186</t>
+          <t>623342242.5987</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>637.213</t>
+          <t>584830672.345477</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>658.994</t>
+          <t>617563834.268473</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>687.691</t>
+          <t>778931680.837106</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>685.484</t>
+          <t>585479711.841645</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>654.219</t>
+          <t>527477451.039699</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>648.912</t>
+          <t>501225742.653579</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>623.683</t>
+          <t>460601391.989989</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>584.262</t>
+          <t>473006767.000585</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>569.793</t>
+          <t>509644726.591272</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>423.511</t>
+          <t>-2146.72043588925</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>436.468</t>
+          <t>-1888.92030523402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>446.083</t>
+          <t>-2065.8347715022</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>458.106</t>
+          <t>-1917.17174995449</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>462.009</t>
+          <t>-1985.89854099127</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>472.919</t>
+          <t>-2160.61525703186</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>497.108</t>
+          <t>-2623.88464117343</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>519.421</t>
+          <t>-3023.89012729993</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>556.486</t>
+          <t>-5143.385029166</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>554.817</t>
+          <t>-3119.02221911051</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>557.869</t>
+          <t>-3392.17761600891</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>560.349</t>
+          <t>-2758.99451613643</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>-2169.97643439031</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>506.844</t>
+          <t>-1752.52849202003</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>492.319</t>
+          <t>-1720.54679041657</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>557.219</t>
+          <t>-426271702.173176</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>646.947</t>
+          <t>-497977809.906987</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>729.198</t>
+          <t>-589758378.907846</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>765.563</t>
+          <t>-615322704.58191</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>688.884</t>
+          <t>-583120369.115014</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>674.669</t>
+          <t>-558702178.575763</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>623.622</t>
+          <t>-526592936.221098</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>662.343</t>
+          <t>-546604713.411612</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>794.808</t>
+          <t>-703107800.144029</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>695.143</t>
+          <t>-531226707.101218</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>632.873</t>
+          <t>-474026105.824203</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>617.869</t>
+          <t>-452435966.781802</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>558.049</t>
+          <t>-410098566.036311</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>531.535</t>
+          <t>-419926798.224688</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>437.662</t>
+          <t>-437068077.0989</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3479.10884</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3508.03582558788</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3932.59290803866</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4982.936</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5770.99103086411</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6074.19391230983</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6466.42463551306</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7487.63941536972</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>8707.03607595372</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>7894.52264274238</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>7418.05855699242</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>7670.07405466714</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6792.59089302969</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6323.26412510346</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5826.22480622937</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>222.547</t>
+          <t>0.142267588635016</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>225.415</t>
+          <t>0.146587987162856</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>225.472</t>
+          <t>0.138725533092411</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>250.43</t>
+          <t>0.135372601398712</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>249.793</t>
+          <t>0.136825378032473</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>253.083</t>
+          <t>0.136791624950318</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>253.318</t>
+          <t>0.140224966864534</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>261.566</t>
+          <t>0.145592896480575</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>264.958</t>
+          <t>0.146009254401994</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>264.502</t>
+          <t>0.141615064453025</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>252.915</t>
+          <t>0.131171072517277</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>240.924</t>
+          <t>0.13616997366602</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>224.839</t>
+          <t>0.139575776303749</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>202.809</t>
+          <t>0.136214484028816</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>193.479</t>
+          <t>0.130355697301868</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3965.12589487155</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4083.26485042669</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4654.34206235087</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6080.74941449745</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>7151.31062921035</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>7664.24291363173</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>8299.32260718529</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>9621.60230544449</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>11094.9724453315</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>10751.7799173601</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>11952.3438223168</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>12937.4205930857</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>11649.4486067851</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>10911.2762094501</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>10240.3864255101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>253.945</t>
+          <t>4991.96707756152</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>283.639</t>
+          <t>5134.56383525791</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>343.046</t>
+          <t>5790.87773499578</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>397.968</t>
+          <t>7607.16169062565</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>393.254</t>
+          <t>8977.88368506092</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>384.272</t>
+          <t>9630.49494735292</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>359.05</t>
+          <t>10275.5101594481</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>353.06</t>
+          <t>11764.4272802749</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>415.609</t>
+          <t>13198.5071455725</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>367.623</t>
+          <t>12699.9225987404</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>369.801</t>
+          <t>13275.5502349952</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>359.275</t>
+          <t>14304.2066275393</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>325.3</t>
+          <t>12872.0079293832</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>316.624</t>
+          <t>12095.8211885877</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>269.754</t>
+          <t>11488.1237643192</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>29661.0580100393</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>30051.6760931552</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>33346.1213783102</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>41113.9197689739</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>48864.1877031138</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>52795.347969346</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>57185.9760614962</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>66427.8852070619</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>78948.1446462889</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>75840.8956615264</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>50.86</t>
+          <t>74824.8657112741</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>55.97</t>
+          <t>78445.0829796137</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>71941.2256023233</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>73285.144235548</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>82.51</t>
+          <t>73360.0148954629</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>6337.54533274899</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>6613.05313541717</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>7091.99097935425</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>7671.2027482921</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.253</t>
+          <t>7960.70341729494</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>8218.92343569712</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>8411.03285664642</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>8671.65593706818</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>8699.38310579365</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>8720.17554830507</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>9440.45204576786</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>9415.83136528337</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>9055.31777744397</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>8282.10027653133</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>8121.09202550589</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5142.67903857607</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5340.39406195979</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5758.2995312518</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>6129.7949309338</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6334.0280944548</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6545.26533077989</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6811.40779565041</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>7113.10217187478</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7355.75179728267</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7423.69194283449</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>8499.55991862338</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>8508.82227391464</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>8185.91174836186</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>7459.4280578568</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>7226.81279672046</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4219.80719945161</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4405.21470936574</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4625.95846477033</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5565.69827282393</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6685.86095472825</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>7221.96143854429</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>8018.90159833932</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>9671.42821437528</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>11527.1597362254</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10740.2133272822</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>9814.85788630902</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>10681.8648835628</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>10041.2524116874</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>9982.49810902255</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>9562.89589577348</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>423511000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>436468000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>446083000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>458106000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>462009000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>472919000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>497108000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>519421000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>556486000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>554817000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>557869000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>560349000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>540638000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>506844000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>492319000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>555556242.970919</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>570023427.894466</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>575896979.567662</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>609002916.645095</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>609513318.417661</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>620186207.799252</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>637213172.101122</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>658994487.580266</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>687690966.878056</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>685483539.768268</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>654219114.287671</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>648911877.178525</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>623683069.56722</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>584262131.77472</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>569793363.988517</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>222547086.021874</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>225414930.769334</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>225471585.33269</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>250430368.838078</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>249793130.458101</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>253082650.205455</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>253317815.882089</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>261565858.469471</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>264958413.31652</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>264502487.591403</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>252914913.403677</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>240923810.904615</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>224839162.55024</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>202809297.510654</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>193478537.56124</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>316400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>323510</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>330460</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>342550</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>356140</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>368510</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>375380</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>388690</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>396310</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>394460</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>401280</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>403460</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>388970</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>365010</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>357510</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>242940</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>249610</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>257020</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>264350</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>275680</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>286930</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>297860</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>311840</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>325260</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>323920</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>353150</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>356900</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>344440</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>313350</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>555556242.970919</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>570023427.894466</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>575896979.567662</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>609002916.645095</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>609513318.417661</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>620186207.799252</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>637213172.101122</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>658994487.580266</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>687690966.878056</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>685483539.768268</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>654219114.287671</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>648911877.178525</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>623683069.56722</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>584262131.77472</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>569793363.988517</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>423511000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>436468000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>446083000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>458106000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>462009000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>472919000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>497108000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>519421000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>556486000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>554817000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>557869000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>560349000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>540638000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>506844000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>492319000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>17663.3882</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>18084.5165410274</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>19763.488076634</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24850.31472</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>28880.0921413263</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>30791.3212220929</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>33766.8827217683</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>40105.9717238383</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>46766.3991117324</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>44133.1795034204</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>42607.7346783981</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>46063.3318177726</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>42409.3166015849</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>41653.3976637709</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>39448.2629837531</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9211.89404</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9539.77606102738</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10416.988556634</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>13172.93712</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>15663.5302513263</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>16852.3004120929</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>18294.6261617683</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>21436.1984238383</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>24725.5786317324</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>23440.2056634204</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>23090.7792783981</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>24986.3638177726</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>22913.6329215849</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>22078.9301937709</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>21050.9211352384</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>45869.7066177866</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>46822.3360694428</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>47602.2778059846</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>47034.5509753314</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>48065.2107030045</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>48463.2084391642</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>50040.6941692544</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>51935.4289773745</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>55061.3402756165</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>53141.3758545459</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>53209.0104100915</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>52005.9327132751</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>51184.7338675637</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>52755.0922374017</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>55871.356388478</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
